--- a/artfynd/S 2313-2020 artfynd.xlsx
+++ b/artfynd/S 2313-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ56"/>
+  <dimension ref="A1:AZ57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1553,10 +1553,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>80474157</v>
+        <v>136976892</v>
       </c>
       <c r="B9" t="n">
-        <v>93199</v>
+        <v>106464</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,37 +1564,50 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>788</v>
+        <v>340</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Igelbacken, Upl</t>
+          <t>Österändan, 300 m N om, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>713678</v>
+        <v>713938</v>
       </c>
       <c r="R9" t="n">
-        <v>6639333</v>
+        <v>6639120</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1621,12 +1634,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2019-10-10</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2019-10-10</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gallringen har medfört ökat ljusinsläpp vilket är positivt. Färre skott i år och ingen hade blommat. Beståndet är mycket litet numera och kan lätt försvinna.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1639,27 +1667,32 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Liten äldre grusgrop i kanten av äldre skogsbilväg i en luckig, förra året gallrad betesgranskog.</t>
+        </is>
+      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80474157</t>
+          <t>https://artportalen.se/Sighting/136976892</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>80474225</v>
+        <v>80474157</v>
       </c>
       <c r="B10" t="n">
         <v>93199</v>
@@ -1697,10 +1730,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>713628</v>
+        <v>713678</v>
       </c>
       <c r="R10" t="n">
-        <v>6639334</v>
+        <v>6639333</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1759,50 +1792,42 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80474225</t>
+          <t>https://artportalen.se/Sighting/80474157</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>80474276</v>
+        <v>80474225</v>
       </c>
       <c r="B11" t="n">
-        <v>93207</v>
+        <v>93199</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Raggtaggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum mirabile</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1811,10 +1836,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>713723</v>
+        <v>713628</v>
       </c>
       <c r="R11" t="n">
-        <v>6639161</v>
+        <v>6639334</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1873,42 +1898,50 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80474276</t>
+          <t>https://artportalen.se/Sighting/80474225</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>80474265</v>
+        <v>80474276</v>
       </c>
       <c r="B12" t="n">
-        <v>91436</v>
+        <v>93207</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1357</v>
+        <v>789</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Raggtaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Hydnellum mirabile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1917,10 +1950,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>713659</v>
+        <v>713723</v>
       </c>
       <c r="R12" t="n">
-        <v>6639234</v>
+        <v>6639161</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1979,38 +2012,38 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80474265</t>
+          <t>https://artportalen.se/Sighting/80474276</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>80474247</v>
+        <v>80474265</v>
       </c>
       <c r="B13" t="n">
-        <v>93205</v>
+        <v>91436</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2058</v>
+        <v>1357</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2023,10 +2056,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>713674</v>
+        <v>713659</v>
       </c>
       <c r="R13" t="n">
-        <v>6639302</v>
+        <v>6639234</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2085,13 +2118,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80474247</t>
+          <t>https://artportalen.se/Sighting/80474265</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>80474370</v>
+        <v>80474247</v>
       </c>
       <c r="B14" t="n">
         <v>93205</v>
@@ -2129,10 +2162,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>713872</v>
+        <v>713674</v>
       </c>
       <c r="R14" t="n">
-        <v>6639094</v>
+        <v>6639302</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2191,13 +2224,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80474370</t>
+          <t>https://artportalen.se/Sighting/80474247</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104197961</v>
+        <v>80474370</v>
       </c>
       <c r="B15" t="n">
         <v>93205</v>
@@ -2231,17 +2264,17 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Österändan, NNW om, Upl</t>
+          <t>Igelbacken, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>713673</v>
+        <v>713872</v>
       </c>
       <c r="R15" t="n">
-        <v>6639297</v>
+        <v>6639094</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2265,12 +2298,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-09-10</t>
+          <t>2019-10-10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-09-10</t>
+          <t>2019-10-10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2286,28 +2319,24 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll, Isak Isaksson, Mats Nordin</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104197961</t>
+          <t>https://artportalen.se/Sighting/80474370</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112255945</v>
+        <v>104197961</v>
       </c>
       <c r="B16" t="n">
         <v>93205</v>
@@ -2336,21 +2365,19 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Österändan, strax N om, Upl</t>
+          <t>Österändan, NNW om, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>713921</v>
+        <v>713673</v>
       </c>
       <c r="R16" t="n">
-        <v>6639116</v>
+        <v>6639297</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2377,17 +2404,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2022-09-10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rödbrun hatt med små fjäll I centrum. Sporer knöliga 4.8-6 um inkl knölar. En stor, gammal svamp observerades.</t>
+          <t>2022-09-10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2396,79 +2418,81 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Kristoffer Stighäll, Isak Isaksson, Mats Nordin</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112255945</t>
+          <t>https://artportalen.se/Sighting/104197961</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>80474436</v>
+        <v>112255945</v>
       </c>
       <c r="B17" t="n">
-        <v>93213</v>
+        <v>93205</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Igelbacken, Upl</t>
+          <t>Österändan, strax N om, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>713871</v>
+        <v>713921</v>
       </c>
       <c r="R17" t="n">
-        <v>6639311</v>
+        <v>6639116</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2492,12 +2516,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2019-10-10</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2019-10-10</t>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rödbrun hatt med små fjäll I centrum. Sporer knöliga 4.8-6 um inkl knölar. En stor, gammal svamp observerades.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2506,62 +2535,65 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Jan Yngve Andersson, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80474436</t>
+          <t>https://artportalen.se/Sighting/112255945</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>80474388</v>
+        <v>80474436</v>
       </c>
       <c r="B18" t="n">
-        <v>96708</v>
+        <v>93213</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>2059</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2569,10 +2601,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>713879</v>
+        <v>713871</v>
       </c>
       <c r="R18" t="n">
-        <v>6639238</v>
+        <v>6639311</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2631,13 +2663,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80474388</t>
+          <t>https://artportalen.se/Sighting/80474436</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>80474399</v>
+        <v>80474388</v>
       </c>
       <c r="B19" t="n">
         <v>96708</v>
@@ -2676,10 +2708,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>713870</v>
+        <v>713879</v>
       </c>
       <c r="R19" t="n">
-        <v>6639252</v>
+        <v>6639238</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2714,11 +2746,6 @@
           <t>2019-10-10</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Flera stora mosskuddar.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2743,16 +2770,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80474399</t>
+          <t>https://artportalen.se/Sighting/80474388</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>80474817</v>
+        <v>80474399</v>
       </c>
       <c r="B20" t="n">
-        <v>87309</v>
+        <v>96708</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2760,26 +2787,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3674</v>
+        <v>2180</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2787,10 +2815,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>713754</v>
+        <v>713870</v>
       </c>
       <c r="R20" t="n">
-        <v>6639335</v>
+        <v>6639252</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2825,6 +2853,11 @@
           <t>2019-10-10</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Flera stora mosskuddar.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2849,38 +2882,38 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80474817</t>
+          <t>https://artportalen.se/Sighting/80474399</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>80473037</v>
+        <v>80474817</v>
       </c>
       <c r="B21" t="n">
-        <v>93189</v>
+        <v>87309</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4361</v>
+        <v>3674</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2893,10 +2926,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>713832</v>
+        <v>713754</v>
       </c>
       <c r="R21" t="n">
-        <v>6639123</v>
+        <v>6639335</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2955,13 +2988,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80473037</t>
+          <t>https://artportalen.se/Sighting/80474817</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>80473928</v>
+        <v>80473037</v>
       </c>
       <c r="B22" t="n">
         <v>93189</v>
@@ -2999,10 +3032,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>713865</v>
+        <v>713832</v>
       </c>
       <c r="R22" t="n">
-        <v>6639216</v>
+        <v>6639123</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3061,13 +3094,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80473928</t>
+          <t>https://artportalen.se/Sighting/80473037</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>80474027</v>
+        <v>80473928</v>
       </c>
       <c r="B23" t="n">
         <v>93189</v>
@@ -3105,10 +3138,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>713778</v>
+        <v>713865</v>
       </c>
       <c r="R23" t="n">
-        <v>6639220</v>
+        <v>6639216</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3167,13 +3200,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80474027</t>
+          <t>https://artportalen.se/Sighting/80473928</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>80474141</v>
+        <v>80474027</v>
       </c>
       <c r="B24" t="n">
         <v>93189</v>
@@ -3211,10 +3244,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>713744</v>
+        <v>713778</v>
       </c>
       <c r="R24" t="n">
-        <v>6639312</v>
+        <v>6639220</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3249,11 +3282,6 @@
           <t>2019-10-10</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Allmänt förekommande inom området.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3278,13 +3306,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80474141</t>
+          <t>https://artportalen.se/Sighting/80474027</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>80474185</v>
+        <v>80474141</v>
       </c>
       <c r="B25" t="n">
         <v>93189</v>
@@ -3322,10 +3350,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>713687</v>
+        <v>713744</v>
       </c>
       <c r="R25" t="n">
-        <v>6639372</v>
+        <v>6639312</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3362,7 +3390,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Allmänt förekommande.</t>
+          <t>Allmänt förekommande inom området.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3389,13 +3417,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80474185</t>
+          <t>https://artportalen.se/Sighting/80474141</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>80474240</v>
+        <v>80474185</v>
       </c>
       <c r="B26" t="n">
         <v>93189</v>
@@ -3433,10 +3461,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>713653</v>
+        <v>713687</v>
       </c>
       <c r="R26" t="n">
-        <v>6639303</v>
+        <v>6639372</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3500,13 +3528,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80474240</t>
+          <t>https://artportalen.se/Sighting/80474185</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>80474590</v>
+        <v>80474240</v>
       </c>
       <c r="B27" t="n">
         <v>93189</v>
@@ -3544,10 +3572,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>713929</v>
+        <v>713653</v>
       </c>
       <c r="R27" t="n">
-        <v>6639209</v>
+        <v>6639303</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3582,6 +3610,11 @@
           <t>2019-10-10</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Allmänt förekommande.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3606,13 +3639,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80474590</t>
+          <t>https://artportalen.se/Sighting/80474240</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>80474596</v>
+        <v>80474590</v>
       </c>
       <c r="B28" t="n">
         <v>93189</v>
@@ -3650,10 +3683,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>713921</v>
+        <v>713929</v>
       </c>
       <c r="R28" t="n">
-        <v>6639198</v>
+        <v>6639209</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3688,11 +3721,6 @@
           <t>2019-10-10</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Allmänt förekommande.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3717,16 +3745,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80474596</t>
+          <t>https://artportalen.se/Sighting/80474590</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>80474286</v>
+        <v>80474596</v>
       </c>
       <c r="B29" t="n">
-        <v>93197</v>
+        <v>93189</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3734,21 +3762,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3761,10 +3789,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>713713</v>
+        <v>713921</v>
       </c>
       <c r="R29" t="n">
-        <v>6639128</v>
+        <v>6639198</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3799,6 +3827,11 @@
           <t>2019-10-10</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Allmänt förekommande.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3823,13 +3856,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80474286</t>
+          <t>https://artportalen.se/Sighting/80474596</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>80474474</v>
+        <v>80474286</v>
       </c>
       <c r="B30" t="n">
         <v>93197</v>
@@ -3867,10 +3900,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>713913</v>
+        <v>713713</v>
       </c>
       <c r="R30" t="n">
-        <v>6639324</v>
+        <v>6639128</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3929,16 +3962,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80474474</t>
+          <t>https://artportalen.se/Sighting/80474286</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>80474208</v>
+        <v>80474474</v>
       </c>
       <c r="B31" t="n">
-        <v>93209</v>
+        <v>93197</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3946,21 +3979,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3973,10 +4006,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>713694</v>
+        <v>713913</v>
       </c>
       <c r="R31" t="n">
-        <v>6639375</v>
+        <v>6639324</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4035,13 +4068,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80474208</t>
+          <t>https://artportalen.se/Sighting/80474474</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>80474301</v>
+        <v>80474208</v>
       </c>
       <c r="B32" t="n">
         <v>93209</v>
@@ -4079,10 +4112,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>713714</v>
+        <v>713694</v>
       </c>
       <c r="R32" t="n">
-        <v>6639099</v>
+        <v>6639375</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4141,16 +4174,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80474301</t>
+          <t>https://artportalen.se/Sighting/80474208</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>80474535</v>
+        <v>80474301</v>
       </c>
       <c r="B33" t="n">
-        <v>91930</v>
+        <v>93209</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4158,21 +4191,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5442</v>
+        <v>4366</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4185,10 +4218,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>713893</v>
+        <v>713714</v>
       </c>
       <c r="R33" t="n">
-        <v>6639285</v>
+        <v>6639099</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4247,16 +4280,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80474535</t>
+          <t>https://artportalen.se/Sighting/80474301</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128420341</v>
+        <v>80474535</v>
       </c>
       <c r="B34" t="n">
-        <v>91409</v>
+        <v>91930</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4264,37 +4297,40 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5741</v>
+        <v>5442</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kåstaskogen, Upl</t>
+          <t>Igelbacken, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>713754</v>
+        <v>713893</v>
       </c>
       <c r="R34" t="n">
-        <v>6639344</v>
+        <v>6639285</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4318,12 +4354,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2019-10-10</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2019-10-10</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4332,33 +4368,34 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128420341</t>
+          <t>https://artportalen.se/Sighting/80474535</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>80472543</v>
+        <v>128420341</v>
       </c>
       <c r="B35" t="n">
-        <v>93233</v>
+        <v>91409</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4366,40 +4403,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5964</v>
+        <v>5741</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Igelbacken, Upl</t>
+          <t>Kåstaskogen, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>713877</v>
+        <v>713754</v>
       </c>
       <c r="R35" t="n">
-        <v>6639083</v>
+        <v>6639344</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4423,12 +4457,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2019-10-10</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2019-10-10</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4437,31 +4471,30 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80472543</t>
+          <t>https://artportalen.se/Sighting/128420341</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>80473048</v>
+        <v>80472543</v>
       </c>
       <c r="B36" t="n">
         <v>93233</v>
@@ -4499,10 +4532,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>713813</v>
+        <v>713877</v>
       </c>
       <c r="R36" t="n">
-        <v>6639103</v>
+        <v>6639083</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4561,13 +4594,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80473048</t>
+          <t>https://artportalen.se/Sighting/80472543</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>80474209</v>
+        <v>80473048</v>
       </c>
       <c r="B37" t="n">
         <v>93233</v>
@@ -4605,10 +4638,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>713694</v>
+        <v>713813</v>
       </c>
       <c r="R37" t="n">
-        <v>6639375</v>
+        <v>6639103</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4667,13 +4700,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80474209</t>
+          <t>https://artportalen.se/Sighting/80473048</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>80474826</v>
+        <v>80474209</v>
       </c>
       <c r="B38" t="n">
         <v>93233</v>
@@ -4711,10 +4744,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>713749</v>
+        <v>713694</v>
       </c>
       <c r="R38" t="n">
-        <v>6639346</v>
+        <v>6639375</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4773,13 +4806,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80474826</t>
+          <t>https://artportalen.se/Sighting/80474209</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>96485532</v>
+        <v>80474826</v>
       </c>
       <c r="B39" t="n">
         <v>93233</v>
@@ -4817,10 +4850,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>713855</v>
+        <v>713749</v>
       </c>
       <c r="R39" t="n">
-        <v>6639207</v>
+        <v>6639346</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4847,22 +4880,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2021-09-26</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>15:42</t>
+          <t>2019-10-10</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2021-09-26</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>16:18</t>
+          <t>2019-10-10</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4875,35 +4898,30 @@
       <c r="AG39" t="b">
         <v>0</v>
       </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Luckig, äldre betesgranskog</t>
-        </is>
-      </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96485532</t>
+          <t>https://artportalen.se/Sighting/80474826</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>80473820</v>
+        <v>96485532</v>
       </c>
       <c r="B40" t="n">
-        <v>93235</v>
+        <v>93233</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4911,21 +4929,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5966</v>
+        <v>5964</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4938,10 +4956,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>713859</v>
+        <v>713855</v>
       </c>
       <c r="R40" t="n">
-        <v>6639201</v>
+        <v>6639207</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4968,12 +4986,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2019-10-10</t>
+          <t>2021-09-26</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2019-10-10</t>
+          <t>2021-09-26</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4986,27 +5014,32 @@
       <c r="AG40" t="b">
         <v>0</v>
       </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Luckig, äldre betesgranskog</t>
+        </is>
+      </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80473820</t>
+          <t>https://artportalen.se/Sighting/96485532</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>80474446</v>
+        <v>80473820</v>
       </c>
       <c r="B41" t="n">
         <v>93235</v>
@@ -5044,10 +5077,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>713862</v>
+        <v>713859</v>
       </c>
       <c r="R41" t="n">
-        <v>6639289</v>
+        <v>6639201</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5106,13 +5139,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80474446</t>
+          <t>https://artportalen.se/Sighting/80473820</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>80474453</v>
+        <v>80474446</v>
       </c>
       <c r="B42" t="n">
         <v>93235</v>
@@ -5150,10 +5183,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>713879</v>
+        <v>713862</v>
       </c>
       <c r="R42" t="n">
-        <v>6639251</v>
+        <v>6639289</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5212,13 +5245,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80474453</t>
+          <t>https://artportalen.se/Sighting/80474446</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>80474460</v>
+        <v>80474453</v>
       </c>
       <c r="B43" t="n">
         <v>93235</v>
@@ -5256,10 +5289,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>713876</v>
+        <v>713879</v>
       </c>
       <c r="R43" t="n">
-        <v>6639233</v>
+        <v>6639251</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5318,13 +5351,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80474460</t>
+          <t>https://artportalen.se/Sighting/80474453</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>80474545</v>
+        <v>80474460</v>
       </c>
       <c r="B44" t="n">
         <v>93235</v>
@@ -5362,10 +5395,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>713897</v>
+        <v>713876</v>
       </c>
       <c r="R44" t="n">
-        <v>6639240</v>
+        <v>6639233</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5424,13 +5457,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80474545</t>
+          <t>https://artportalen.se/Sighting/80474460</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>80474565</v>
+        <v>80474545</v>
       </c>
       <c r="B45" t="n">
         <v>93235</v>
@@ -5468,10 +5501,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>713917</v>
+        <v>713897</v>
       </c>
       <c r="R45" t="n">
-        <v>6639221</v>
+        <v>6639240</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5530,13 +5563,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80474565</t>
+          <t>https://artportalen.se/Sighting/80474545</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>80474573</v>
+        <v>80474565</v>
       </c>
       <c r="B46" t="n">
         <v>93235</v>
@@ -5574,10 +5607,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>713939</v>
+        <v>713917</v>
       </c>
       <c r="R46" t="n">
-        <v>6639216</v>
+        <v>6639221</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5636,13 +5669,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80474573</t>
+          <t>https://artportalen.se/Sighting/80474565</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>80474603</v>
+        <v>80474573</v>
       </c>
       <c r="B47" t="n">
         <v>93235</v>
@@ -5680,10 +5713,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>713923</v>
+        <v>713939</v>
       </c>
       <c r="R47" t="n">
-        <v>6639168</v>
+        <v>6639216</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5742,49 +5775,43 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80474603</t>
+          <t>https://artportalen.se/Sighting/80474573</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>80474216</v>
+        <v>80474603</v>
       </c>
       <c r="B48" t="n">
-        <v>5179</v>
+        <v>93235</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100526</v>
+        <v>5966</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5792,10 +5819,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>713635</v>
+        <v>713923</v>
       </c>
       <c r="R48" t="n">
-        <v>6639339</v>
+        <v>6639168</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5854,13 +5881,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80474216</t>
+          <t>https://artportalen.se/Sighting/80474603</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>80474467</v>
+        <v>80474216</v>
       </c>
       <c r="B49" t="n">
         <v>5179</v>
@@ -5904,10 +5931,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>713902</v>
+        <v>713635</v>
       </c>
       <c r="R49" t="n">
-        <v>6639332</v>
+        <v>6639339</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5960,22 +5987,22 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Via Bo Törnquist</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80474467</t>
+          <t>https://artportalen.se/Sighting/80474216</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>80962820</v>
+        <v>80474467</v>
       </c>
       <c r="B50" t="n">
-        <v>58592</v>
+        <v>5179</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5983,45 +6010,43 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>102125</v>
+        <v>100526</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>rastande</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Österändan, skogsbilväg N om, Upl</t>
+          <t>Igelbacken, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>713894</v>
+        <v>713902</v>
       </c>
       <c r="R50" t="n">
-        <v>6639072</v>
+        <v>6639332</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6048,27 +6073,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2019-11-23</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>13:55</t>
+          <t>2019-10-10</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2019-11-23</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Minst tre ex sitter i grantoppar och flöjtar för fullt.</t>
+          <t>2019-10-10</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6077,33 +6087,34 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Via Bo Törnquist</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80962820</t>
+          <t>https://artportalen.se/Sighting/80474467</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>80472573</v>
+        <v>80962820</v>
       </c>
       <c r="B51" t="n">
-        <v>57947</v>
+        <v>58592</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6111,46 +6122,45 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>102977</v>
+        <v>102125</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Igelbacken, Upl</t>
+          <t>Österändan, skogsbilväg N om, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>713877</v>
+        <v>713894</v>
       </c>
       <c r="R51" t="n">
-        <v>6639083</v>
+        <v>6639072</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6177,12 +6187,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2019-10-10</t>
+          <t>2019-11-23</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2019-10-10</t>
+          <t>2019-11-23</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Minst tre ex sitter i grantoppar och flöjtar för fullt.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6197,27 +6222,27 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80472573</t>
+          <t>https://artportalen.se/Sighting/80962820</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>80474523</v>
+        <v>80472573</v>
       </c>
       <c r="B52" t="n">
-        <v>5199</v>
+        <v>57947</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6225,30 +6250,33 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>105930</v>
+        <v>102977</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -6258,10 +6286,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>713914</v>
+        <v>713877</v>
       </c>
       <c r="R52" t="n">
-        <v>6639311</v>
+        <v>6639083</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6302,7 +6330,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6320,16 +6347,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80474523</t>
+          <t>https://artportalen.se/Sighting/80472573</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>80474149</v>
+        <v>80474523</v>
       </c>
       <c r="B53" t="n">
-        <v>106244</v>
+        <v>5199</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6337,27 +6364,32 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221144</v>
+        <v>105930</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6365,10 +6397,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>713701</v>
+        <v>713914</v>
       </c>
       <c r="R53" t="n">
-        <v>6639328</v>
+        <v>6639311</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6427,13 +6459,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80474149</t>
+          <t>https://artportalen.se/Sighting/80474523</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>112255944</v>
+        <v>80474149</v>
       </c>
       <c r="B54" t="n">
         <v>106244</v>
@@ -6462,24 +6494,23 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Österändan, strax N om, Upl</t>
+          <t>Igelbacken, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>713916</v>
+        <v>713701</v>
       </c>
       <c r="R54" t="n">
-        <v>6639113</v>
+        <v>6639328</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6503,17 +6534,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2019-10-10</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ett litet bestånd.</t>
+          <t>2019-10-10</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6522,87 +6548,77 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112255944</t>
+          <t>https://artportalen.se/Sighting/80474149</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>80474174</v>
+        <v>112255944</v>
       </c>
       <c r="B55" t="n">
-        <v>91428</v>
+        <v>106244</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>256756</v>
+        <v>221144</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blek fingersvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramaria pallida</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schaeff.) Ricken</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Igelbacken, Upl</t>
+          <t>Österändan, strax N om, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>713690</v>
+        <v>713916</v>
       </c>
       <c r="R55" t="n">
-        <v>6639356</v>
+        <v>6639113</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6626,12 +6642,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2019-10-10</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2019-10-10</t>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ett litet bestånd.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6640,34 +6661,38 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Jan Yngve Andersson, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80474174</t>
+          <t>https://artportalen.se/Sighting/112255944</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>80473966</v>
+        <v>80474174</v>
       </c>
       <c r="B56" t="n">
-        <v>87346</v>
+        <v>91428</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6675,25 +6700,33 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6003295</v>
+        <v>256756</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blek fingersvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria pallida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+          <t>(Schaeff.) Ricken</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
@@ -6702,10 +6735,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>713794</v>
+        <v>713690</v>
       </c>
       <c r="R56" t="n">
-        <v>6639225</v>
+        <v>6639356</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6763,6 +6796,112 @@
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80474174</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>80473966</v>
+      </c>
+      <c r="B57" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Igelbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>713794</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6639225</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Roslags-Bro</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2019-10-10</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2019-10-10</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/80473966</t>
         </is>
@@ -6825,6 +6964,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 2313-2020 artfynd.xlsx
+++ b/artfynd/S 2313-2020 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>136976892</v>
       </c>
       <c r="B9" t="n">
-        <v>106464</v>
+        <v>106470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 2313-2020 artfynd.xlsx
+++ b/artfynd/S 2313-2020 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>136976892</v>
       </c>
       <c r="B9" t="n">
-        <v>106470</v>
+        <v>106474</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 2313-2020 artfynd.xlsx
+++ b/artfynd/S 2313-2020 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>136976892</v>
       </c>
       <c r="B9" t="n">
-        <v>106474</v>
+        <v>106476</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 2313-2020 artfynd.xlsx
+++ b/artfynd/S 2313-2020 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>136976892</v>
       </c>
       <c r="B9" t="n">
-        <v>106476</v>
+        <v>106478</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 2313-2020 artfynd.xlsx
+++ b/artfynd/S 2313-2020 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>136976892</v>
       </c>
       <c r="B9" t="n">
-        <v>106478</v>
+        <v>106491</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 2313-2020 artfynd.xlsx
+++ b/artfynd/S 2313-2020 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>136976892</v>
       </c>
       <c r="B9" t="n">
-        <v>106491</v>
+        <v>106493</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 2313-2020 artfynd.xlsx
+++ b/artfynd/S 2313-2020 artfynd.xlsx
@@ -1591,11 +1591,7 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">

--- a/artfynd/S 2313-2020 artfynd.xlsx
+++ b/artfynd/S 2313-2020 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>136976892</v>
       </c>
       <c r="B9" t="n">
-        <v>106493</v>
+        <v>106497</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 2313-2020 artfynd.xlsx
+++ b/artfynd/S 2313-2020 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>136976892</v>
       </c>
       <c r="B9" t="n">
-        <v>106497</v>
+        <v>106516</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 2313-2020 artfynd.xlsx
+++ b/artfynd/S 2313-2020 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>136976892</v>
       </c>
       <c r="B9" t="n">
-        <v>106516</v>
+        <v>106517</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 2313-2020 artfynd.xlsx
+++ b/artfynd/S 2313-2020 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>136976892</v>
       </c>
       <c r="B9" t="n">
-        <v>106517</v>
+        <v>106522</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 2313-2020 artfynd.xlsx
+++ b/artfynd/S 2313-2020 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>136976892</v>
       </c>
       <c r="B9" t="n">
-        <v>106522</v>
+        <v>106525</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 2313-2020 artfynd.xlsx
+++ b/artfynd/S 2313-2020 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>136976892</v>
       </c>
       <c r="B9" t="n">
-        <v>106525</v>
+        <v>106531</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 2313-2020 artfynd.xlsx
+++ b/artfynd/S 2313-2020 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>136976892</v>
       </c>
       <c r="B9" t="n">
-        <v>106531</v>
+        <v>106532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 2313-2020 artfynd.xlsx
+++ b/artfynd/S 2313-2020 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>136976892</v>
       </c>
       <c r="B9" t="n">
-        <v>106532</v>
+        <v>106544</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 2313-2020 artfynd.xlsx
+++ b/artfynd/S 2313-2020 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>136976892</v>
       </c>
       <c r="B9" t="n">
-        <v>106544</v>
+        <v>106545</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 2313-2020 artfynd.xlsx
+++ b/artfynd/S 2313-2020 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>136976892</v>
       </c>
       <c r="B9" t="n">
-        <v>106545</v>
+        <v>106548</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 2313-2020 artfynd.xlsx
+++ b/artfynd/S 2313-2020 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>136976892</v>
       </c>
       <c r="B9" t="n">
-        <v>106548</v>
+        <v>106554</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
